--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_12-03-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_12-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="261">
   <si>
     <t>SKU</t>
   </si>
@@ -619,10 +619,13 @@
     <t>£20.11</t>
   </si>
   <si>
+    <t>£21.74</t>
+  </si>
+  <si>
     <t>£25.31</t>
   </si>
   <si>
-    <t>£28.79</t>
+    <t>£32.41</t>
   </si>
   <si>
     <t>£42.60</t>
@@ -640,16 +643,13 @@
     <t>£81.47</t>
   </si>
   <si>
-    <t>£86.41</t>
-  </si>
-  <si>
     <t>£90.32</t>
   </si>
   <si>
     <t>£88.72</t>
   </si>
   <si>
-    <t>£476.10</t>
+    <t>£416.25</t>
   </si>
   <si>
     <t>£515.52</t>
@@ -722,6 +722,9 @@
   </si>
   <si>
     <t>£22.20</t>
+  </si>
+  <si>
+    <t>£25.28</t>
   </si>
   <si>
     <t>£26.54</t>
@@ -1263,7 +1266,7 @@
         <v>230</v>
       </c>
       <c r="R2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1307,7 +1310,7 @@
         <v>186</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="O3" t="s">
         <v>213</v>
@@ -1319,7 +1322,7 @@
         <v>231</v>
       </c>
       <c r="R3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1375,7 +1378,7 @@
         <v>232</v>
       </c>
       <c r="R4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1431,7 +1434,7 @@
         <v>233</v>
       </c>
       <c r="R5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1487,7 +1490,7 @@
         <v>234</v>
       </c>
       <c r="R6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1531,7 +1534,7 @@
         <v>190</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="O7" t="s">
         <v>216</v>
@@ -1543,7 +1546,7 @@
         <v>217</v>
       </c>
       <c r="R7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1587,7 +1590,7 @@
         <v>191</v>
       </c>
       <c r="N8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O8" t="s">
         <v>217</v>
@@ -1599,7 +1602,7 @@
         <v>235</v>
       </c>
       <c r="R8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1643,7 +1646,7 @@
         <v>192</v>
       </c>
       <c r="N9" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="O9" t="s">
         <v>218</v>
@@ -1652,10 +1655,10 @@
         <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>88</v>
+        <v>236</v>
       </c>
       <c r="R9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1699,7 +1702,7 @@
         <v>89</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="O10" t="s">
         <v>219</v>
@@ -1708,10 +1711,10 @@
         <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1755,7 +1758,7 @@
         <v>193</v>
       </c>
       <c r="N11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O11" t="s">
         <v>220</v>
@@ -1764,10 +1767,10 @@
         <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1811,7 +1814,7 @@
         <v>194</v>
       </c>
       <c r="N12" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="O12" t="s">
         <v>221</v>
@@ -1820,7 +1823,7 @@
         <v>88</v>
       </c>
       <c r="Q12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R12" t="s">
         <v>89</v>
@@ -1867,7 +1870,7 @@
         <v>195</v>
       </c>
       <c r="N13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O13" t="s">
         <v>222</v>
@@ -1876,10 +1879,10 @@
         <v>88</v>
       </c>
       <c r="Q13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1923,7 +1926,7 @@
         <v>196</v>
       </c>
       <c r="N14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O14" t="s">
         <v>223</v>
@@ -1932,7 +1935,7 @@
         <v>88</v>
       </c>
       <c r="Q14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R14" t="s">
         <v>89</v>
@@ -1979,7 +1982,7 @@
         <v>197</v>
       </c>
       <c r="N15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O15" t="s">
         <v>224</v>
@@ -1988,7 +1991,7 @@
         <v>88</v>
       </c>
       <c r="Q15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R15" t="s">
         <v>89</v>
@@ -2044,10 +2047,10 @@
         <v>88</v>
       </c>
       <c r="Q16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2159,7 +2162,7 @@
         <v>89</v>
       </c>
       <c r="R18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2215,7 +2218,7 @@
         <v>89</v>
       </c>
       <c r="R19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2439,7 +2442,7 @@
         <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2495,7 +2498,7 @@
         <v>89</v>
       </c>
       <c r="R24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2551,7 +2554,7 @@
         <v>89</v>
       </c>
       <c r="R25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
